--- a/astro-site/public/dl/kit-tareas-pasteleria/02-partidas-cocina.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/02-partidas-cocina.xlsx
@@ -1929,7 +1929,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Almíbar a 118-121 °C · mantequilla a 18-20 °C</t>
+          <t>Italiano: almíbar a 118-121 °C · suizo: claras y azúcar a 71 °C · mantequilla a 18-20 °C</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
